--- a/hall/resources/sample/BuyOneGetSeven.xlsx
+++ b/hall/resources/sample/BuyOneGetSeven.xlsx
@@ -89,7 +89,7 @@
     <t>1990000_1000000|1980000_200|1024001_20000</t>
   </si>
   <si>
-    <t>1202502_10</t>
+    <t>1022502_10</t>
   </si>
   <si>
     <t>1990000_2000000</t>

--- a/hall/resources/sample/BuyOneGetSeven.xlsx
+++ b/hall/resources/sample/BuyOneGetSeven.xlsx
@@ -101,7 +101,7 @@
     <t>1990000_3000000</t>
   </si>
   <si>
-    <t>1024001_20</t>
+    <t>1024001_5000</t>
   </si>
   <si>
     <t>1990000_4000000</t>
